--- a/public/exports-from-60-with-coowners/29189447.xlsx
+++ b/public/exports-from-60-with-coowners/29189447.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042618</t>
+          <t xml:space="preserve">200042632</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -18589,12 +18589,12 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911471</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24514,12 +24514,12 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -24589,12 +24589,12 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
